--- a/artfynd/A 8397-2025 artfynd.xlsx
+++ b/artfynd/A 8397-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127700039</v>
       </c>
       <c r="B2" t="n">
-        <v>91740</v>
+        <v>91742</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127700020</v>
+        <v>127700017</v>
       </c>
       <c r="B3" t="n">
-        <v>91737</v>
+        <v>57660</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,29 +783,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6040186</v>
+        <v>100049</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Stöverberget, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>784942</v>
+        <v>784699</v>
       </c>
       <c r="R3" t="n">
-        <v>7184210</v>
+        <v>7184415</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -838,6 +851,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -864,10 +882,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127700017</v>
+        <v>127700020</v>
       </c>
       <c r="B4" t="n">
-        <v>57658</v>
+        <v>91739</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -875,42 +893,29 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Stöverberget, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>784699</v>
+        <v>784942</v>
       </c>
       <c r="R4" t="n">
-        <v>7184415</v>
+        <v>7184210</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -943,11 +948,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -977,7 +977,7 @@
         <v>127700032</v>
       </c>
       <c r="B5" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1074,7 +1074,7 @@
         <v>127700012</v>
       </c>
       <c r="B6" t="n">
-        <v>91330</v>
+        <v>91332</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         <v>127700009</v>
       </c>
       <c r="B7" t="n">
-        <v>91688</v>
+        <v>91690</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>127700036</v>
       </c>
       <c r="B8" t="n">
-        <v>91326</v>
+        <v>91328</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         <v>127700035</v>
       </c>
       <c r="B9" t="n">
-        <v>91326</v>
+        <v>91328</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
         <v>127700029</v>
       </c>
       <c r="B10" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         <v>127700024</v>
       </c>
       <c r="B11" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         <v>127700016</v>
       </c>
       <c r="B12" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
         <v>127700026</v>
       </c>
       <c r="B13" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
         <v>127700030</v>
       </c>
       <c r="B14" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1956,7 +1956,7 @@
         <v>127700025</v>
       </c>
       <c r="B15" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
         <v>127700021</v>
       </c>
       <c r="B16" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 8397-2025 artfynd.xlsx
+++ b/artfynd/A 8397-2025 artfynd.xlsx
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127700017</v>
+        <v>127700020</v>
       </c>
       <c r="B3" t="n">
-        <v>57660</v>
+        <v>91739</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,42 +783,29 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Stöverberget, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>784699</v>
+        <v>784942</v>
       </c>
       <c r="R3" t="n">
-        <v>7184415</v>
+        <v>7184210</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -851,11 +838,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -882,10 +864,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127700020</v>
+        <v>127700017</v>
       </c>
       <c r="B4" t="n">
-        <v>91739</v>
+        <v>57660</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -893,29 +875,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6040186</v>
+        <v>100049</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Stöverberget, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>784942</v>
+        <v>784699</v>
       </c>
       <c r="R4" t="n">
-        <v>7184210</v>
+        <v>7184415</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -948,6 +943,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -974,10 +974,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127700032</v>
+        <v>127700009</v>
       </c>
       <c r="B5" t="n">
-        <v>98450</v>
+        <v>91690</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -985,21 +985,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>2062</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1009,10 +1009,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>784810</v>
+        <v>784860</v>
       </c>
       <c r="R5" t="n">
-        <v>7184264</v>
+        <v>7184233</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1053,6 +1053,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1168,10 +1169,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127700009</v>
+        <v>127700032</v>
       </c>
       <c r="B7" t="n">
-        <v>91690</v>
+        <v>98450</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1179,21 +1180,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2062</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1203,10 +1204,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>784860</v>
+        <v>784810</v>
       </c>
       <c r="R7" t="n">
-        <v>7184233</v>
+        <v>7184264</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1247,7 +1248,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1460,45 +1460,53 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127700029</v>
+        <v>127700016</v>
       </c>
       <c r="B10" t="n">
-        <v>98450</v>
+        <v>57660</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Stöverberget, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>784899</v>
+        <v>784815</v>
       </c>
       <c r="R10" t="n">
-        <v>7184293</v>
+        <v>7184343</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1557,7 +1565,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127700024</v>
+        <v>127700029</v>
       </c>
       <c r="B11" t="n">
         <v>98450</v>
@@ -1592,10 +1600,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>784893</v>
+        <v>784899</v>
       </c>
       <c r="R11" t="n">
-        <v>7184231</v>
+        <v>7184293</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1654,53 +1662,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127700016</v>
+        <v>127700024</v>
       </c>
       <c r="B12" t="n">
-        <v>57660</v>
+        <v>98450</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Stöverberget, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>784815</v>
+        <v>784893</v>
       </c>
       <c r="R12" t="n">
-        <v>7184343</v>
+        <v>7184231</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 8397-2025 artfynd.xlsx
+++ b/artfynd/A 8397-2025 artfynd.xlsx
@@ -974,32 +974,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127700009</v>
+        <v>127700012</v>
       </c>
       <c r="B5" t="n">
-        <v>91690</v>
+        <v>91332</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2062</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1009,10 +1009,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>784860</v>
+        <v>784920</v>
       </c>
       <c r="R5" t="n">
-        <v>7184233</v>
+        <v>7184246</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1053,7 +1053,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1072,32 +1071,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127700012</v>
+        <v>127700009</v>
       </c>
       <c r="B6" t="n">
-        <v>91332</v>
+        <v>91690</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>2062</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1107,10 +1106,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>784920</v>
+        <v>784860</v>
       </c>
       <c r="R6" t="n">
-        <v>7184246</v>
+        <v>7184233</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1151,6 +1150,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 8397-2025 artfynd.xlsx
+++ b/artfynd/A 8397-2025 artfynd.xlsx
@@ -974,32 +974,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127700012</v>
+        <v>127700009</v>
       </c>
       <c r="B5" t="n">
-        <v>91332</v>
+        <v>91690</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>2062</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1009,10 +1009,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>784920</v>
+        <v>784860</v>
       </c>
       <c r="R5" t="n">
-        <v>7184246</v>
+        <v>7184233</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1053,6 +1053,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1071,32 +1072,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127700009</v>
+        <v>127700012</v>
       </c>
       <c r="B6" t="n">
-        <v>91690</v>
+        <v>91332</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2062</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1106,10 +1107,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>784860</v>
+        <v>784920</v>
       </c>
       <c r="R6" t="n">
-        <v>7184233</v>
+        <v>7184246</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1150,7 +1151,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1460,53 +1460,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127700016</v>
+        <v>127700029</v>
       </c>
       <c r="B10" t="n">
-        <v>57660</v>
+        <v>98450</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Stöverberget, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>784815</v>
+        <v>784899</v>
       </c>
       <c r="R10" t="n">
-        <v>7184343</v>
+        <v>7184293</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1565,7 +1557,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127700029</v>
+        <v>127700024</v>
       </c>
       <c r="B11" t="n">
         <v>98450</v>
@@ -1600,10 +1592,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>784899</v>
+        <v>784893</v>
       </c>
       <c r="R11" t="n">
-        <v>7184293</v>
+        <v>7184231</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1662,45 +1654,53 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127700024</v>
+        <v>127700016</v>
       </c>
       <c r="B12" t="n">
-        <v>98450</v>
+        <v>57660</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Stöverberget, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>784893</v>
+        <v>784815</v>
       </c>
       <c r="R12" t="n">
-        <v>7184231</v>
+        <v>7184343</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 8397-2025 artfynd.xlsx
+++ b/artfynd/A 8397-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127700039</v>
       </c>
       <c r="B2" t="n">
-        <v>91742</v>
+        <v>91748</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127700020</v>
+        <v>127700017</v>
       </c>
       <c r="B3" t="n">
-        <v>91739</v>
+        <v>57660</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,29 +783,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6040186</v>
+        <v>100049</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Stöverberget, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>784942</v>
+        <v>784699</v>
       </c>
       <c r="R3" t="n">
-        <v>7184210</v>
+        <v>7184415</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -838,6 +851,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -864,10 +882,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127700017</v>
+        <v>127700020</v>
       </c>
       <c r="B4" t="n">
-        <v>57660</v>
+        <v>91745</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -875,42 +893,29 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Stöverberget, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>784699</v>
+        <v>784942</v>
       </c>
       <c r="R4" t="n">
-        <v>7184415</v>
+        <v>7184210</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -943,11 +948,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -974,32 +974,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127700009</v>
+        <v>127700012</v>
       </c>
       <c r="B5" t="n">
-        <v>91690</v>
+        <v>91338</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2062</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1009,10 +1009,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>784860</v>
+        <v>784920</v>
       </c>
       <c r="R5" t="n">
-        <v>7184233</v>
+        <v>7184246</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1053,7 +1053,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1072,32 +1071,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127700012</v>
+        <v>127700009</v>
       </c>
       <c r="B6" t="n">
-        <v>91332</v>
+        <v>91696</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>2062</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1107,10 +1106,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>784920</v>
+        <v>784860</v>
       </c>
       <c r="R6" t="n">
-        <v>7184246</v>
+        <v>7184233</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1151,6 +1150,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1172,7 +1172,7 @@
         <v>127700032</v>
       </c>
       <c r="B7" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>127700036</v>
       </c>
       <c r="B8" t="n">
-        <v>91328</v>
+        <v>91334</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         <v>127700035</v>
       </c>
       <c r="B9" t="n">
-        <v>91328</v>
+        <v>91334</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
         <v>127700029</v>
       </c>
       <c r="B10" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         <v>127700024</v>
       </c>
       <c r="B11" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
         <v>127700026</v>
       </c>
       <c r="B13" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
         <v>127700030</v>
       </c>
       <c r="B14" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1956,7 +1956,7 @@
         <v>127700025</v>
       </c>
       <c r="B15" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
         <v>127700021</v>
       </c>
       <c r="B16" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 8397-2025 artfynd.xlsx
+++ b/artfynd/A 8397-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127700039</v>
       </c>
       <c r="B2" t="n">
-        <v>91748</v>
+        <v>91751</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127700017</v>
       </c>
       <c r="B3" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         <v>127700020</v>
       </c>
       <c r="B4" t="n">
-        <v>91745</v>
+        <v>91748</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -977,7 +977,7 @@
         <v>127700012</v>
       </c>
       <c r="B5" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1074,7 +1074,7 @@
         <v>127700009</v>
       </c>
       <c r="B6" t="n">
-        <v>91696</v>
+        <v>91699</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         <v>127700032</v>
       </c>
       <c r="B7" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>127700036</v>
       </c>
       <c r="B8" t="n">
-        <v>91334</v>
+        <v>91337</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         <v>127700035</v>
       </c>
       <c r="B9" t="n">
-        <v>91334</v>
+        <v>91337</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1460,45 +1460,53 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127700029</v>
+        <v>127700016</v>
       </c>
       <c r="B10" t="n">
-        <v>98456</v>
+        <v>57663</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Stöverberget, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>784899</v>
+        <v>784815</v>
       </c>
       <c r="R10" t="n">
-        <v>7184293</v>
+        <v>7184343</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1557,10 +1565,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127700024</v>
+        <v>127700029</v>
       </c>
       <c r="B11" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1592,10 +1600,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>784893</v>
+        <v>784899</v>
       </c>
       <c r="R11" t="n">
-        <v>7184231</v>
+        <v>7184293</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1654,53 +1662,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127700016</v>
+        <v>127700024</v>
       </c>
       <c r="B12" t="n">
-        <v>57660</v>
+        <v>98459</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Stöverberget, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>784815</v>
+        <v>784893</v>
       </c>
       <c r="R12" t="n">
-        <v>7184343</v>
+        <v>7184231</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1762,7 +1762,7 @@
         <v>127700026</v>
       </c>
       <c r="B13" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
         <v>127700030</v>
       </c>
       <c r="B14" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1956,7 +1956,7 @@
         <v>127700025</v>
       </c>
       <c r="B15" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
         <v>127700021</v>
       </c>
       <c r="B16" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 8397-2025 artfynd.xlsx
+++ b/artfynd/A 8397-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127700039</v>
       </c>
       <c r="B2" t="n">
-        <v>91751</v>
+        <v>91759</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127700017</v>
       </c>
       <c r="B3" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         <v>127700020</v>
       </c>
       <c r="B4" t="n">
-        <v>91748</v>
+        <v>91756</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -977,7 +977,7 @@
         <v>127700012</v>
       </c>
       <c r="B5" t="n">
-        <v>91341</v>
+        <v>91349</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1074,7 +1074,7 @@
         <v>127700009</v>
       </c>
       <c r="B6" t="n">
-        <v>91699</v>
+        <v>91707</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         <v>127700032</v>
       </c>
       <c r="B7" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>127700036</v>
       </c>
       <c r="B8" t="n">
-        <v>91337</v>
+        <v>91345</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         <v>127700035</v>
       </c>
       <c r="B9" t="n">
-        <v>91337</v>
+        <v>91345</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1460,53 +1460,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127700016</v>
+        <v>127700029</v>
       </c>
       <c r="B10" t="n">
-        <v>57663</v>
+        <v>98467</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Stöverberget, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>784815</v>
+        <v>784899</v>
       </c>
       <c r="R10" t="n">
-        <v>7184343</v>
+        <v>7184293</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1565,10 +1557,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127700029</v>
+        <v>127700024</v>
       </c>
       <c r="B11" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1600,10 +1592,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>784899</v>
+        <v>784893</v>
       </c>
       <c r="R11" t="n">
-        <v>7184293</v>
+        <v>7184231</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1662,45 +1654,53 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127700024</v>
+        <v>127700016</v>
       </c>
       <c r="B12" t="n">
-        <v>98459</v>
+        <v>57669</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Stöverberget, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>784893</v>
+        <v>784815</v>
       </c>
       <c r="R12" t="n">
-        <v>7184231</v>
+        <v>7184343</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1762,7 +1762,7 @@
         <v>127700026</v>
       </c>
       <c r="B13" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
         <v>127700030</v>
       </c>
       <c r="B14" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1956,7 +1956,7 @@
         <v>127700025</v>
       </c>
       <c r="B15" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
         <v>127700021</v>
       </c>
       <c r="B16" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 8397-2025 artfynd.xlsx
+++ b/artfynd/A 8397-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127700039</v>
       </c>
       <c r="B2" t="n">
-        <v>91759</v>
+        <v>91760</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         <v>127700020</v>
       </c>
       <c r="B4" t="n">
-        <v>91756</v>
+        <v>91757</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,32 +974,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127700012</v>
+        <v>127700032</v>
       </c>
       <c r="B5" t="n">
-        <v>91349</v>
+        <v>98468</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1009,10 +1009,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>784920</v>
+        <v>784810</v>
       </c>
       <c r="R5" t="n">
-        <v>7184246</v>
+        <v>7184264</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,32 +1071,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127700009</v>
+        <v>127700012</v>
       </c>
       <c r="B6" t="n">
-        <v>91707</v>
+        <v>91350</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2062</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1106,10 +1106,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>784860</v>
+        <v>784920</v>
       </c>
       <c r="R6" t="n">
-        <v>7184233</v>
+        <v>7184246</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1150,7 +1150,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1169,10 +1168,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127700032</v>
+        <v>127700009</v>
       </c>
       <c r="B7" t="n">
-        <v>98467</v>
+        <v>91708</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1180,21 +1179,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>2062</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1204,10 +1203,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>784810</v>
+        <v>784860</v>
       </c>
       <c r="R7" t="n">
-        <v>7184264</v>
+        <v>7184233</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1248,6 +1247,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1269,7 +1269,7 @@
         <v>127700036</v>
       </c>
       <c r="B8" t="n">
-        <v>91345</v>
+        <v>91346</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         <v>127700035</v>
       </c>
       <c r="B9" t="n">
-        <v>91345</v>
+        <v>91346</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1460,45 +1460,53 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127700029</v>
+        <v>127700016</v>
       </c>
       <c r="B10" t="n">
-        <v>98467</v>
+        <v>57669</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Stöverberget, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>784899</v>
+        <v>784815</v>
       </c>
       <c r="R10" t="n">
-        <v>7184293</v>
+        <v>7184343</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1557,10 +1565,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127700024</v>
+        <v>127700029</v>
       </c>
       <c r="B11" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1592,10 +1600,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>784893</v>
+        <v>784899</v>
       </c>
       <c r="R11" t="n">
-        <v>7184231</v>
+        <v>7184293</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1654,53 +1662,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127700016</v>
+        <v>127700024</v>
       </c>
       <c r="B12" t="n">
-        <v>57669</v>
+        <v>98468</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Stöverberget, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>784815</v>
+        <v>784893</v>
       </c>
       <c r="R12" t="n">
-        <v>7184343</v>
+        <v>7184231</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1762,7 +1762,7 @@
         <v>127700026</v>
       </c>
       <c r="B13" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
         <v>127700030</v>
       </c>
       <c r="B14" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1956,7 +1956,7 @@
         <v>127700025</v>
       </c>
       <c r="B15" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
         <v>127700021</v>
       </c>
       <c r="B16" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 8397-2025 artfynd.xlsx
+++ b/artfynd/A 8397-2025 artfynd.xlsx
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127700017</v>
+        <v>127700020</v>
       </c>
       <c r="B3" t="n">
-        <v>57669</v>
+        <v>91757</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,42 +783,29 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Stöverberget, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>784699</v>
+        <v>784942</v>
       </c>
       <c r="R3" t="n">
-        <v>7184415</v>
+        <v>7184210</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -851,11 +838,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -882,10 +864,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127700020</v>
+        <v>127700017</v>
       </c>
       <c r="B4" t="n">
-        <v>91757</v>
+        <v>57669</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -893,29 +875,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6040186</v>
+        <v>100049</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Stöverberget, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>784942</v>
+        <v>784699</v>
       </c>
       <c r="R4" t="n">
-        <v>7184210</v>
+        <v>7184415</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -948,6 +943,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -974,10 +974,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127700032</v>
+        <v>127700009</v>
       </c>
       <c r="B5" t="n">
-        <v>98468</v>
+        <v>91708</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -985,21 +985,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>2062</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1009,10 +1009,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>784810</v>
+        <v>784860</v>
       </c>
       <c r="R5" t="n">
-        <v>7184264</v>
+        <v>7184233</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1053,6 +1053,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1168,10 +1169,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127700009</v>
+        <v>127700032</v>
       </c>
       <c r="B7" t="n">
-        <v>91708</v>
+        <v>98468</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1179,21 +1180,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2062</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1203,10 +1204,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>784860</v>
+        <v>784810</v>
       </c>
       <c r="R7" t="n">
-        <v>7184233</v>
+        <v>7184264</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1247,7 +1248,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 8397-2025 artfynd.xlsx
+++ b/artfynd/A 8397-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127700039</v>
       </c>
       <c r="B2" t="n">
-        <v>91760</v>
+        <v>91761</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127700020</v>
+        <v>127700017</v>
       </c>
       <c r="B3" t="n">
-        <v>91757</v>
+        <v>57669</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,29 +783,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6040186</v>
+        <v>100049</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Stöverberget, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>784942</v>
+        <v>784699</v>
       </c>
       <c r="R3" t="n">
-        <v>7184210</v>
+        <v>7184415</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -838,6 +851,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -864,10 +882,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127700017</v>
+        <v>127700020</v>
       </c>
       <c r="B4" t="n">
-        <v>57669</v>
+        <v>91758</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -875,42 +893,29 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Stöverberget, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>784699</v>
+        <v>784942</v>
       </c>
       <c r="R4" t="n">
-        <v>7184415</v>
+        <v>7184210</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -943,11 +948,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -977,7 +977,7 @@
         <v>127700009</v>
       </c>
       <c r="B5" t="n">
-        <v>91708</v>
+        <v>91709</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>127700012</v>
       </c>
       <c r="B6" t="n">
-        <v>91350</v>
+        <v>91351</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         <v>127700032</v>
       </c>
       <c r="B7" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>127700036</v>
       </c>
       <c r="B8" t="n">
-        <v>91346</v>
+        <v>91347</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         <v>127700035</v>
       </c>
       <c r="B9" t="n">
-        <v>91346</v>
+        <v>91347</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
         <v>127700029</v>
       </c>
       <c r="B11" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1665,7 +1665,7 @@
         <v>127700024</v>
       </c>
       <c r="B12" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
         <v>127700026</v>
       </c>
       <c r="B13" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
         <v>127700030</v>
       </c>
       <c r="B14" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1956,7 +1956,7 @@
         <v>127700025</v>
       </c>
       <c r="B15" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
         <v>127700021</v>
       </c>
       <c r="B16" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 8397-2025 artfynd.xlsx
+++ b/artfynd/A 8397-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127700039</v>
       </c>
       <c r="B2" t="n">
-        <v>91761</v>
+        <v>91762</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127700017</v>
+        <v>127700020</v>
       </c>
       <c r="B3" t="n">
-        <v>57669</v>
+        <v>91759</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,42 +783,29 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Stöverberget, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>784699</v>
+        <v>784942</v>
       </c>
       <c r="R3" t="n">
-        <v>7184415</v>
+        <v>7184210</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -851,11 +838,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -882,10 +864,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127700020</v>
+        <v>127700017</v>
       </c>
       <c r="B4" t="n">
-        <v>91758</v>
+        <v>57669</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -893,29 +875,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6040186</v>
+        <v>100049</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Stöverberget, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>784942</v>
+        <v>784699</v>
       </c>
       <c r="R4" t="n">
-        <v>7184210</v>
+        <v>7184415</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -948,6 +943,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -974,32 +974,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127700009</v>
+        <v>127700012</v>
       </c>
       <c r="B5" t="n">
-        <v>91709</v>
+        <v>91352</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2062</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1009,10 +1009,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>784860</v>
+        <v>784920</v>
       </c>
       <c r="R5" t="n">
-        <v>7184233</v>
+        <v>7184246</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1053,7 +1053,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1072,32 +1071,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127700012</v>
+        <v>127700009</v>
       </c>
       <c r="B6" t="n">
-        <v>91351</v>
+        <v>91710</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>2062</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1107,10 +1106,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>784920</v>
+        <v>784860</v>
       </c>
       <c r="R6" t="n">
-        <v>7184246</v>
+        <v>7184233</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1151,6 +1150,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1172,7 +1172,7 @@
         <v>127700032</v>
       </c>
       <c r="B7" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>127700036</v>
       </c>
       <c r="B8" t="n">
-        <v>91347</v>
+        <v>91348</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         <v>127700035</v>
       </c>
       <c r="B9" t="n">
-        <v>91347</v>
+        <v>91348</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
         <v>127700029</v>
       </c>
       <c r="B11" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1665,7 +1665,7 @@
         <v>127700024</v>
       </c>
       <c r="B12" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
         <v>127700026</v>
       </c>
       <c r="B13" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
         <v>127700030</v>
       </c>
       <c r="B14" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1956,7 +1956,7 @@
         <v>127700025</v>
       </c>
       <c r="B15" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
         <v>127700021</v>
       </c>
       <c r="B16" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 8397-2025 artfynd.xlsx
+++ b/artfynd/A 8397-2025 artfynd.xlsx
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127700020</v>
+        <v>127700017</v>
       </c>
       <c r="B3" t="n">
-        <v>91759</v>
+        <v>57669</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,29 +783,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6040186</v>
+        <v>100049</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Stöverberget, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>784942</v>
+        <v>784699</v>
       </c>
       <c r="R3" t="n">
-        <v>7184210</v>
+        <v>7184415</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -838,6 +851,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -864,10 +882,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127700017</v>
+        <v>127700020</v>
       </c>
       <c r="B4" t="n">
-        <v>57669</v>
+        <v>91759</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -875,42 +893,29 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Stöverberget, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>784699</v>
+        <v>784942</v>
       </c>
       <c r="R4" t="n">
-        <v>7184415</v>
+        <v>7184210</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -943,11 +948,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -974,32 +974,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127700012</v>
+        <v>127700032</v>
       </c>
       <c r="B5" t="n">
-        <v>91352</v>
+        <v>98470</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1009,10 +1009,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>784920</v>
+        <v>784810</v>
       </c>
       <c r="R5" t="n">
-        <v>7184246</v>
+        <v>7184264</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,32 +1071,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127700009</v>
+        <v>127700012</v>
       </c>
       <c r="B6" t="n">
-        <v>91710</v>
+        <v>91352</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2062</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1106,10 +1106,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>784860</v>
+        <v>784920</v>
       </c>
       <c r="R6" t="n">
-        <v>7184233</v>
+        <v>7184246</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1150,7 +1150,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1169,10 +1168,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127700032</v>
+        <v>127700009</v>
       </c>
       <c r="B7" t="n">
-        <v>98470</v>
+        <v>91710</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1180,21 +1179,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>2062</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1204,10 +1203,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>784810</v>
+        <v>784860</v>
       </c>
       <c r="R7" t="n">
-        <v>7184264</v>
+        <v>7184233</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1248,6 +1247,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1460,53 +1460,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127700016</v>
+        <v>127700029</v>
       </c>
       <c r="B10" t="n">
-        <v>57669</v>
+        <v>98470</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Stöverberget, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>784815</v>
+        <v>784899</v>
       </c>
       <c r="R10" t="n">
-        <v>7184343</v>
+        <v>7184293</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1565,7 +1557,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127700029</v>
+        <v>127700024</v>
       </c>
       <c r="B11" t="n">
         <v>98470</v>
@@ -1600,10 +1592,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>784899</v>
+        <v>784893</v>
       </c>
       <c r="R11" t="n">
-        <v>7184293</v>
+        <v>7184231</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1662,45 +1654,53 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127700024</v>
+        <v>127700016</v>
       </c>
       <c r="B12" t="n">
-        <v>98470</v>
+        <v>57669</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Stöverberget, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>784893</v>
+        <v>784815</v>
       </c>
       <c r="R12" t="n">
-        <v>7184231</v>
+        <v>7184343</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 8397-2025 artfynd.xlsx
+++ b/artfynd/A 8397-2025 artfynd.xlsx
@@ -1460,45 +1460,53 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127700029</v>
+        <v>127700016</v>
       </c>
       <c r="B10" t="n">
-        <v>98470</v>
+        <v>57669</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Stöverberget, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>784899</v>
+        <v>784815</v>
       </c>
       <c r="R10" t="n">
-        <v>7184293</v>
+        <v>7184343</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1557,7 +1565,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127700024</v>
+        <v>127700029</v>
       </c>
       <c r="B11" t="n">
         <v>98470</v>
@@ -1592,10 +1600,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>784893</v>
+        <v>784899</v>
       </c>
       <c r="R11" t="n">
-        <v>7184231</v>
+        <v>7184293</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1654,53 +1662,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127700016</v>
+        <v>127700024</v>
       </c>
       <c r="B12" t="n">
-        <v>57669</v>
+        <v>98470</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Stöverberget, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>784815</v>
+        <v>784893</v>
       </c>
       <c r="R12" t="n">
-        <v>7184343</v>
+        <v>7184231</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 8397-2025 artfynd.xlsx
+++ b/artfynd/A 8397-2025 artfynd.xlsx
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127700017</v>
+        <v>127700020</v>
       </c>
       <c r="B3" t="n">
-        <v>57669</v>
+        <v>91759</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,42 +783,29 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Stöverberget, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>784699</v>
+        <v>784942</v>
       </c>
       <c r="R3" t="n">
-        <v>7184415</v>
+        <v>7184210</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -851,11 +838,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -882,10 +864,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127700020</v>
+        <v>127700017</v>
       </c>
       <c r="B4" t="n">
-        <v>91759</v>
+        <v>57669</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -893,29 +875,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6040186</v>
+        <v>100049</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Stöverberget, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>784942</v>
+        <v>784699</v>
       </c>
       <c r="R4" t="n">
-        <v>7184210</v>
+        <v>7184415</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -948,6 +943,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 8397-2025 artfynd.xlsx
+++ b/artfynd/A 8397-2025 artfynd.xlsx
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127700020</v>
+        <v>127700017</v>
       </c>
       <c r="B3" t="n">
-        <v>91759</v>
+        <v>57669</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,29 +783,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6040186</v>
+        <v>100049</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Stöverberget, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>784942</v>
+        <v>784699</v>
       </c>
       <c r="R3" t="n">
-        <v>7184210</v>
+        <v>7184415</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -838,6 +851,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -864,10 +882,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127700017</v>
+        <v>127700020</v>
       </c>
       <c r="B4" t="n">
-        <v>57669</v>
+        <v>91759</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -875,42 +893,29 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Stöverberget, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>784699</v>
+        <v>784942</v>
       </c>
       <c r="R4" t="n">
-        <v>7184415</v>
+        <v>7184210</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -943,11 +948,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -974,10 +974,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127700032</v>
+        <v>127700009</v>
       </c>
       <c r="B5" t="n">
-        <v>98470</v>
+        <v>91710</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -985,21 +985,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>2062</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1009,10 +1009,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>784810</v>
+        <v>784860</v>
       </c>
       <c r="R5" t="n">
-        <v>7184264</v>
+        <v>7184233</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1053,6 +1053,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1168,10 +1169,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127700009</v>
+        <v>127700032</v>
       </c>
       <c r="B7" t="n">
-        <v>91710</v>
+        <v>98470</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1179,21 +1180,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2062</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1203,10 +1204,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>784860</v>
+        <v>784810</v>
       </c>
       <c r="R7" t="n">
-        <v>7184233</v>
+        <v>7184264</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1247,7 +1248,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1460,53 +1460,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127700016</v>
+        <v>127700029</v>
       </c>
       <c r="B10" t="n">
-        <v>57669</v>
+        <v>98470</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Stöverberget, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>784815</v>
+        <v>784899</v>
       </c>
       <c r="R10" t="n">
-        <v>7184343</v>
+        <v>7184293</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1565,7 +1557,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127700029</v>
+        <v>127700024</v>
       </c>
       <c r="B11" t="n">
         <v>98470</v>
@@ -1600,10 +1592,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>784899</v>
+        <v>784893</v>
       </c>
       <c r="R11" t="n">
-        <v>7184293</v>
+        <v>7184231</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1662,45 +1654,53 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127700024</v>
+        <v>127700016</v>
       </c>
       <c r="B12" t="n">
-        <v>98470</v>
+        <v>57669</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Stöverberget, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>784893</v>
+        <v>784815</v>
       </c>
       <c r="R12" t="n">
-        <v>7184231</v>
+        <v>7184343</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 8397-2025 artfynd.xlsx
+++ b/artfynd/A 8397-2025 artfynd.xlsx
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127700017</v>
+        <v>127700020</v>
       </c>
       <c r="B3" t="n">
-        <v>57669</v>
+        <v>91759</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,42 +783,29 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Stöverberget, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>784699</v>
+        <v>784942</v>
       </c>
       <c r="R3" t="n">
-        <v>7184415</v>
+        <v>7184210</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -851,11 +838,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -882,10 +864,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127700020</v>
+        <v>127700017</v>
       </c>
       <c r="B4" t="n">
-        <v>91759</v>
+        <v>57669</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -893,29 +875,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6040186</v>
+        <v>100049</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Stöverberget, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>784942</v>
+        <v>784699</v>
       </c>
       <c r="R4" t="n">
-        <v>7184210</v>
+        <v>7184415</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -948,6 +943,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1460,45 +1460,53 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127700029</v>
+        <v>127700016</v>
       </c>
       <c r="B10" t="n">
-        <v>98470</v>
+        <v>57669</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Stöverberget, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>784899</v>
+        <v>784815</v>
       </c>
       <c r="R10" t="n">
-        <v>7184293</v>
+        <v>7184343</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1557,7 +1565,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127700024</v>
+        <v>127700029</v>
       </c>
       <c r="B11" t="n">
         <v>98470</v>
@@ -1592,10 +1600,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>784893</v>
+        <v>784899</v>
       </c>
       <c r="R11" t="n">
-        <v>7184231</v>
+        <v>7184293</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1654,53 +1662,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127700016</v>
+        <v>127700024</v>
       </c>
       <c r="B12" t="n">
-        <v>57669</v>
+        <v>98470</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Stöverberget, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>784815</v>
+        <v>784893</v>
       </c>
       <c r="R12" t="n">
-        <v>7184343</v>
+        <v>7184231</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 8397-2025 artfynd.xlsx
+++ b/artfynd/A 8397-2025 artfynd.xlsx
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127700020</v>
+        <v>127700017</v>
       </c>
       <c r="B3" t="n">
-        <v>91759</v>
+        <v>57669</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,29 +783,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6040186</v>
+        <v>100049</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Stöverberget, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>784942</v>
+        <v>784699</v>
       </c>
       <c r="R3" t="n">
-        <v>7184210</v>
+        <v>7184415</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -838,6 +851,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -864,10 +882,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127700017</v>
+        <v>127700020</v>
       </c>
       <c r="B4" t="n">
-        <v>57669</v>
+        <v>91759</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -875,42 +893,29 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Stöverberget, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>784699</v>
+        <v>784942</v>
       </c>
       <c r="R4" t="n">
-        <v>7184415</v>
+        <v>7184210</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -943,11 +948,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -974,10 +974,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127700009</v>
+        <v>127700032</v>
       </c>
       <c r="B5" t="n">
-        <v>91710</v>
+        <v>98470</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -985,21 +985,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2062</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1009,10 +1009,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>784860</v>
+        <v>784810</v>
       </c>
       <c r="R5" t="n">
-        <v>7184233</v>
+        <v>7184264</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1053,7 +1053,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1169,10 +1168,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127700032</v>
+        <v>127700009</v>
       </c>
       <c r="B7" t="n">
-        <v>98470</v>
+        <v>91710</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1180,21 +1179,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>2062</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1204,10 +1203,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>784810</v>
+        <v>784860</v>
       </c>
       <c r="R7" t="n">
-        <v>7184264</v>
+        <v>7184233</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1248,6 +1247,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1460,53 +1460,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127700016</v>
+        <v>127700029</v>
       </c>
       <c r="B10" t="n">
-        <v>57669</v>
+        <v>98470</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Stöverberget, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>784815</v>
+        <v>784899</v>
       </c>
       <c r="R10" t="n">
-        <v>7184343</v>
+        <v>7184293</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1565,7 +1557,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127700029</v>
+        <v>127700024</v>
       </c>
       <c r="B11" t="n">
         <v>98470</v>
@@ -1600,10 +1592,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>784899</v>
+        <v>784893</v>
       </c>
       <c r="R11" t="n">
-        <v>7184293</v>
+        <v>7184231</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1662,45 +1654,53 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127700024</v>
+        <v>127700016</v>
       </c>
       <c r="B12" t="n">
-        <v>98470</v>
+        <v>57669</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Stöverberget, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>784893</v>
+        <v>784815</v>
       </c>
       <c r="R12" t="n">
-        <v>7184231</v>
+        <v>7184343</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 8397-2025 artfynd.xlsx
+++ b/artfynd/A 8397-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127700039</v>
       </c>
       <c r="B2" t="n">
-        <v>91762</v>
+        <v>91770</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127700017</v>
+        <v>127700020</v>
       </c>
       <c r="B3" t="n">
-        <v>57669</v>
+        <v>91767</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,42 +783,29 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Stöverberget, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>784699</v>
+        <v>784942</v>
       </c>
       <c r="R3" t="n">
-        <v>7184415</v>
+        <v>7184210</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -851,11 +838,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -882,10 +864,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127700020</v>
+        <v>127700017</v>
       </c>
       <c r="B4" t="n">
-        <v>91759</v>
+        <v>57670</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -893,29 +875,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6040186</v>
+        <v>100049</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Stöverberget, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>784942</v>
+        <v>784699</v>
       </c>
       <c r="R4" t="n">
-        <v>7184210</v>
+        <v>7184415</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -948,6 +943,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -977,7 +977,7 @@
         <v>127700032</v>
       </c>
       <c r="B5" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1074,7 +1074,7 @@
         <v>127700012</v>
       </c>
       <c r="B6" t="n">
-        <v>91352</v>
+        <v>91360</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         <v>127700009</v>
       </c>
       <c r="B7" t="n">
-        <v>91710</v>
+        <v>91718</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>127700036</v>
       </c>
       <c r="B8" t="n">
-        <v>91348</v>
+        <v>91356</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         <v>127700035</v>
       </c>
       <c r="B9" t="n">
-        <v>91348</v>
+        <v>91356</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1460,45 +1460,53 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127700029</v>
+        <v>127700016</v>
       </c>
       <c r="B10" t="n">
-        <v>98470</v>
+        <v>57670</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Stöverberget, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>784899</v>
+        <v>784815</v>
       </c>
       <c r="R10" t="n">
-        <v>7184293</v>
+        <v>7184343</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1557,10 +1565,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127700024</v>
+        <v>127700029</v>
       </c>
       <c r="B11" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1592,10 +1600,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>784893</v>
+        <v>784899</v>
       </c>
       <c r="R11" t="n">
-        <v>7184231</v>
+        <v>7184293</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1654,53 +1662,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127700016</v>
+        <v>127700024</v>
       </c>
       <c r="B12" t="n">
-        <v>57669</v>
+        <v>98478</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Stöverberget, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>784815</v>
+        <v>784893</v>
       </c>
       <c r="R12" t="n">
-        <v>7184343</v>
+        <v>7184231</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1762,7 +1762,7 @@
         <v>127700026</v>
       </c>
       <c r="B13" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
         <v>127700030</v>
       </c>
       <c r="B14" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1956,7 +1956,7 @@
         <v>127700025</v>
       </c>
       <c r="B15" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
         <v>127700021</v>
       </c>
       <c r="B16" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 8397-2025 artfynd.xlsx
+++ b/artfynd/A 8397-2025 artfynd.xlsx
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127700020</v>
+        <v>127700017</v>
       </c>
       <c r="B3" t="n">
-        <v>91767</v>
+        <v>57670</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,29 +783,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6040186</v>
+        <v>100049</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Stöverberget, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>784942</v>
+        <v>784699</v>
       </c>
       <c r="R3" t="n">
-        <v>7184210</v>
+        <v>7184415</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -838,6 +851,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -864,10 +882,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127700017</v>
+        <v>127700020</v>
       </c>
       <c r="B4" t="n">
-        <v>57670</v>
+        <v>91767</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -875,42 +893,29 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Stöverberget, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>784699</v>
+        <v>784942</v>
       </c>
       <c r="R4" t="n">
-        <v>7184415</v>
+        <v>7184210</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -943,11 +948,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 8397-2025 artfynd.xlsx
+++ b/artfynd/A 8397-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127700039</v>
       </c>
       <c r="B2" t="n">
-        <v>91770</v>
+        <v>91781</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127700017</v>
       </c>
       <c r="B3" t="n">
-        <v>57670</v>
+        <v>57681</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         <v>127700020</v>
       </c>
       <c r="B4" t="n">
-        <v>91767</v>
+        <v>91778</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,32 +974,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127700032</v>
+        <v>127700012</v>
       </c>
       <c r="B5" t="n">
-        <v>98478</v>
+        <v>91371</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1009,10 +1009,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>784810</v>
+        <v>784920</v>
       </c>
       <c r="R5" t="n">
-        <v>7184264</v>
+        <v>7184246</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,32 +1071,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127700012</v>
+        <v>127700009</v>
       </c>
       <c r="B6" t="n">
-        <v>91360</v>
+        <v>91729</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>2062</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1106,10 +1106,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>784920</v>
+        <v>784860</v>
       </c>
       <c r="R6" t="n">
-        <v>7184246</v>
+        <v>7184233</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1150,6 +1150,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1168,10 +1169,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127700009</v>
+        <v>127700032</v>
       </c>
       <c r="B7" t="n">
-        <v>91718</v>
+        <v>98490</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1179,21 +1180,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2062</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1203,10 +1204,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>784860</v>
+        <v>784810</v>
       </c>
       <c r="R7" t="n">
-        <v>7184233</v>
+        <v>7184264</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1247,7 +1248,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1269,7 +1269,7 @@
         <v>127700036</v>
       </c>
       <c r="B8" t="n">
-        <v>91356</v>
+        <v>91367</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         <v>127700035</v>
       </c>
       <c r="B9" t="n">
-        <v>91356</v>
+        <v>91367</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
         <v>127700016</v>
       </c>
       <c r="B10" t="n">
-        <v>57670</v>
+        <v>57681</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
         <v>127700029</v>
       </c>
       <c r="B11" t="n">
-        <v>98478</v>
+        <v>98490</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1665,7 +1665,7 @@
         <v>127700024</v>
       </c>
       <c r="B12" t="n">
-        <v>98478</v>
+        <v>98490</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
         <v>127700026</v>
       </c>
       <c r="B13" t="n">
-        <v>98478</v>
+        <v>98490</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
         <v>127700030</v>
       </c>
       <c r="B14" t="n">
-        <v>98478</v>
+        <v>98490</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1956,7 +1956,7 @@
         <v>127700025</v>
       </c>
       <c r="B15" t="n">
-        <v>98478</v>
+        <v>98490</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
         <v>127700021</v>
       </c>
       <c r="B16" t="n">
-        <v>98478</v>
+        <v>98490</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 8397-2025 artfynd.xlsx
+++ b/artfynd/A 8397-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127700039</v>
       </c>
       <c r="B2" t="n">
-        <v>91781</v>
+        <v>91914</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -768,14 +768,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
         <v>127700017</v>
       </c>
       <c r="B3" t="n">
-        <v>57681</v>
+        <v>57713</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -878,14 +882,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
         <v>127700020</v>
       </c>
       <c r="B4" t="n">
-        <v>91778</v>
+        <v>91911</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -970,14 +978,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr"/>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
         <v>127700012</v>
       </c>
       <c r="B5" t="n">
-        <v>91371</v>
+        <v>91504</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1067,14 +1079,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr"/>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
         <v>127700009</v>
       </c>
       <c r="B6" t="n">
-        <v>91729</v>
+        <v>91862</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1165,14 +1181,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY6" t="inlineStr"/>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
         <v>127700032</v>
       </c>
       <c r="B7" t="n">
-        <v>98490</v>
+        <v>98632</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1262,14 +1282,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY7" t="inlineStr"/>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
         <v>127700036</v>
       </c>
       <c r="B8" t="n">
-        <v>91367</v>
+        <v>91500</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1359,14 +1383,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY8" t="inlineStr"/>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
         <v>127700035</v>
       </c>
       <c r="B9" t="n">
-        <v>91367</v>
+        <v>91500</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1456,14 +1484,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY9" t="inlineStr"/>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
         <v>127700016</v>
       </c>
       <c r="B10" t="n">
-        <v>57681</v>
+        <v>57713</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1561,14 +1593,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY10" t="inlineStr"/>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
         <v>127700029</v>
       </c>
       <c r="B11" t="n">
-        <v>98490</v>
+        <v>98632</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1658,14 +1694,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY11" t="inlineStr"/>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
         <v>127700024</v>
       </c>
       <c r="B12" t="n">
-        <v>98490</v>
+        <v>98632</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1755,14 +1795,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY12" t="inlineStr"/>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
         <v>127700026</v>
       </c>
       <c r="B13" t="n">
-        <v>98490</v>
+        <v>98632</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1852,14 +1896,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY13" t="inlineStr"/>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
         <v>127700030</v>
       </c>
       <c r="B14" t="n">
-        <v>98490</v>
+        <v>98632</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1949,14 +1997,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY14" t="inlineStr"/>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
         <v>127700025</v>
       </c>
       <c r="B15" t="n">
-        <v>98490</v>
+        <v>98632</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2046,14 +2098,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY15" t="inlineStr"/>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
         <v>127700021</v>
       </c>
       <c r="B16" t="n">
-        <v>98490</v>
+        <v>98632</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2143,7 +2199,11 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY16" t="inlineStr"/>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 8397-2025 artfynd.xlsx
+++ b/artfynd/A 8397-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127700039</v>
       </c>
       <c r="B2" t="n">
-        <v>91914</v>
+        <v>91918</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127700017</v>
       </c>
       <c r="B3" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>127700020</v>
       </c>
       <c r="B4" t="n">
-        <v>91911</v>
+        <v>91915</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>127700012</v>
       </c>
       <c r="B5" t="n">
-        <v>91504</v>
+        <v>91508</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
         <v>127700009</v>
       </c>
       <c r="B6" t="n">
-        <v>91862</v>
+        <v>91866</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
         <v>127700032</v>
       </c>
       <c r="B7" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         <v>127700036</v>
       </c>
       <c r="B8" t="n">
-        <v>91500</v>
+        <v>91504</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1394,7 +1394,7 @@
         <v>127700035</v>
       </c>
       <c r="B9" t="n">
-        <v>91500</v>
+        <v>91504</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>127700016</v>
       </c>
       <c r="B10" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
         <v>127700029</v>
       </c>
       <c r="B11" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1705,7 +1705,7 @@
         <v>127700024</v>
       </c>
       <c r="B12" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1806,7 +1806,7 @@
         <v>127700026</v>
       </c>
       <c r="B13" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>127700030</v>
       </c>
       <c r="B14" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2008,7 +2008,7 @@
         <v>127700025</v>
       </c>
       <c r="B15" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2109,7 +2109,7 @@
         <v>127700021</v>
       </c>
       <c r="B16" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 8397-2025 artfynd.xlsx
+++ b/artfynd/A 8397-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127700039</v>
       </c>
       <c r="B2" t="n">
-        <v>91918</v>
+        <v>91923</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127700017</v>
       </c>
       <c r="B3" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>127700020</v>
       </c>
       <c r="B4" t="n">
-        <v>91915</v>
+        <v>91920</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>127700012</v>
       </c>
       <c r="B5" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
         <v>127700009</v>
       </c>
       <c r="B6" t="n">
-        <v>91866</v>
+        <v>91871</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
         <v>127700032</v>
       </c>
       <c r="B7" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         <v>127700036</v>
       </c>
       <c r="B8" t="n">
-        <v>91504</v>
+        <v>91509</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1394,7 +1394,7 @@
         <v>127700035</v>
       </c>
       <c r="B9" t="n">
-        <v>91504</v>
+        <v>91509</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>127700016</v>
       </c>
       <c r="B10" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
         <v>127700029</v>
       </c>
       <c r="B11" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1705,7 +1705,7 @@
         <v>127700024</v>
       </c>
       <c r="B12" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1806,7 +1806,7 @@
         <v>127700026</v>
       </c>
       <c r="B13" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>127700030</v>
       </c>
       <c r="B14" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2008,7 +2008,7 @@
         <v>127700025</v>
       </c>
       <c r="B15" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2109,7 +2109,7 @@
         <v>127700021</v>
       </c>
       <c r="B16" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 8397-2025 artfynd.xlsx
+++ b/artfynd/A 8397-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127700039</v>
       </c>
       <c r="B2" t="n">
-        <v>91931</v>
+        <v>91934</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>127700020</v>
       </c>
       <c r="B4" t="n">
-        <v>91928</v>
+        <v>91931</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>127700012</v>
       </c>
       <c r="B5" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
         <v>127700009</v>
       </c>
       <c r="B6" t="n">
-        <v>91879</v>
+        <v>91882</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
         <v>127700032</v>
       </c>
       <c r="B7" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         <v>127700036</v>
       </c>
       <c r="B8" t="n">
-        <v>91516</v>
+        <v>91519</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1394,7 +1394,7 @@
         <v>127700035</v>
       </c>
       <c r="B9" t="n">
-        <v>91516</v>
+        <v>91519</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
         <v>127700029</v>
       </c>
       <c r="B11" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1705,7 +1705,7 @@
         <v>127700024</v>
       </c>
       <c r="B12" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1806,7 +1806,7 @@
         <v>127700026</v>
       </c>
       <c r="B13" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>127700030</v>
       </c>
       <c r="B14" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2008,7 +2008,7 @@
         <v>127700025</v>
       </c>
       <c r="B15" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2109,7 +2109,7 @@
         <v>127700021</v>
       </c>
       <c r="B16" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 8397-2025 artfynd.xlsx
+++ b/artfynd/A 8397-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127700039</v>
       </c>
       <c r="B2" t="n">
-        <v>91934</v>
+        <v>91937</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>127700020</v>
       </c>
       <c r="B4" t="n">
-        <v>91931</v>
+        <v>91934</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>127700012</v>
       </c>
       <c r="B5" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
         <v>127700009</v>
       </c>
       <c r="B6" t="n">
-        <v>91882</v>
+        <v>91885</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
         <v>127700032</v>
       </c>
       <c r="B7" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         <v>127700036</v>
       </c>
       <c r="B8" t="n">
-        <v>91519</v>
+        <v>91522</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1394,7 +1394,7 @@
         <v>127700035</v>
       </c>
       <c r="B9" t="n">
-        <v>91519</v>
+        <v>91522</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
         <v>127700029</v>
       </c>
       <c r="B11" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1705,7 +1705,7 @@
         <v>127700024</v>
       </c>
       <c r="B12" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1806,7 +1806,7 @@
         <v>127700026</v>
       </c>
       <c r="B13" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>127700030</v>
       </c>
       <c r="B14" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2008,7 +2008,7 @@
         <v>127700025</v>
       </c>
       <c r="B15" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2109,7 +2109,7 @@
         <v>127700021</v>
       </c>
       <c r="B16" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 8397-2025 artfynd.xlsx
+++ b/artfynd/A 8397-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127700039</v>
       </c>
       <c r="B2" t="n">
-        <v>91937</v>
+        <v>91944</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127700017</v>
       </c>
       <c r="B3" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>127700020</v>
       </c>
       <c r="B4" t="n">
-        <v>91934</v>
+        <v>91941</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>127700012</v>
       </c>
       <c r="B5" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
         <v>127700009</v>
       </c>
       <c r="B6" t="n">
-        <v>91885</v>
+        <v>91892</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
         <v>127700032</v>
       </c>
       <c r="B7" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         <v>127700036</v>
       </c>
       <c r="B8" t="n">
-        <v>91522</v>
+        <v>91529</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1394,7 +1394,7 @@
         <v>127700035</v>
       </c>
       <c r="B9" t="n">
-        <v>91522</v>
+        <v>91529</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>127700016</v>
       </c>
       <c r="B10" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
         <v>127700029</v>
       </c>
       <c r="B11" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1705,7 +1705,7 @@
         <v>127700024</v>
       </c>
       <c r="B12" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1806,7 +1806,7 @@
         <v>127700026</v>
       </c>
       <c r="B13" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>127700030</v>
       </c>
       <c r="B14" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2008,7 +2008,7 @@
         <v>127700025</v>
       </c>
       <c r="B15" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2109,7 +2109,7 @@
         <v>127700021</v>
       </c>
       <c r="B16" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 8397-2025 artfynd.xlsx
+++ b/artfynd/A 8397-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127700039</v>
       </c>
       <c r="B2" t="n">
-        <v>91944</v>
+        <v>91951</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>127700020</v>
       </c>
       <c r="B4" t="n">
-        <v>91941</v>
+        <v>91948</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>127700012</v>
       </c>
       <c r="B5" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
         <v>127700009</v>
       </c>
       <c r="B6" t="n">
-        <v>91892</v>
+        <v>91899</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
         <v>127700032</v>
       </c>
       <c r="B7" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         <v>127700036</v>
       </c>
       <c r="B8" t="n">
-        <v>91529</v>
+        <v>91536</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1394,7 +1394,7 @@
         <v>127700035</v>
       </c>
       <c r="B9" t="n">
-        <v>91529</v>
+        <v>91536</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
         <v>127700029</v>
       </c>
       <c r="B11" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1705,7 +1705,7 @@
         <v>127700024</v>
       </c>
       <c r="B12" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1806,7 +1806,7 @@
         <v>127700026</v>
       </c>
       <c r="B13" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>127700030</v>
       </c>
       <c r="B14" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2008,7 +2008,7 @@
         <v>127700025</v>
       </c>
       <c r="B15" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2109,7 +2109,7 @@
         <v>127700021</v>
       </c>
       <c r="B16" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 8397-2025 artfynd.xlsx
+++ b/artfynd/A 8397-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127700039</v>
       </c>
       <c r="B2" t="n">
-        <v>91951</v>
+        <v>91953</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127700017</v>
       </c>
       <c r="B3" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>127700020</v>
       </c>
       <c r="B4" t="n">
-        <v>91948</v>
+        <v>91950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>127700012</v>
       </c>
       <c r="B5" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
         <v>127700009</v>
       </c>
       <c r="B6" t="n">
-        <v>91899</v>
+        <v>91901</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
         <v>127700032</v>
       </c>
       <c r="B7" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         <v>127700036</v>
       </c>
       <c r="B8" t="n">
-        <v>91536</v>
+        <v>91538</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1394,7 +1394,7 @@
         <v>127700035</v>
       </c>
       <c r="B9" t="n">
-        <v>91536</v>
+        <v>91538</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>127700016</v>
       </c>
       <c r="B10" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
         <v>127700029</v>
       </c>
       <c r="B11" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1705,7 +1705,7 @@
         <v>127700024</v>
       </c>
       <c r="B12" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1806,7 +1806,7 @@
         <v>127700026</v>
       </c>
       <c r="B13" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>127700030</v>
       </c>
       <c r="B14" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2008,7 +2008,7 @@
         <v>127700025</v>
       </c>
       <c r="B15" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2109,7 +2109,7 @@
         <v>127700021</v>
       </c>
       <c r="B16" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 8397-2025 artfynd.xlsx
+++ b/artfynd/A 8397-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127700039</v>
       </c>
       <c r="B2" t="n">
-        <v>91953</v>
+        <v>91962</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>127700020</v>
       </c>
       <c r="B4" t="n">
-        <v>91950</v>
+        <v>91958</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>127700012</v>
       </c>
       <c r="B5" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
         <v>127700009</v>
       </c>
       <c r="B6" t="n">
-        <v>91901</v>
+        <v>91910</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
         <v>127700032</v>
       </c>
       <c r="B7" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         <v>127700036</v>
       </c>
       <c r="B8" t="n">
-        <v>91538</v>
+        <v>91536</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1394,7 +1394,7 @@
         <v>127700035</v>
       </c>
       <c r="B9" t="n">
-        <v>91538</v>
+        <v>91536</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
         <v>127700029</v>
       </c>
       <c r="B11" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1705,7 +1705,7 @@
         <v>127700024</v>
       </c>
       <c r="B12" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1806,7 +1806,7 @@
         <v>127700026</v>
       </c>
       <c r="B13" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>127700030</v>
       </c>
       <c r="B14" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2008,7 +2008,7 @@
         <v>127700025</v>
       </c>
       <c r="B15" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2109,7 +2109,7 @@
         <v>127700021</v>
       </c>
       <c r="B16" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 8397-2025 artfynd.xlsx
+++ b/artfynd/A 8397-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127700039</v>
       </c>
       <c r="B2" t="n">
-        <v>91962</v>
+        <v>91963</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>127700020</v>
       </c>
       <c r="B4" t="n">
-        <v>91958</v>
+        <v>91959</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
         <v>127700009</v>
       </c>
       <c r="B6" t="n">
-        <v>91910</v>
+        <v>91911</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
         <v>127700032</v>
       </c>
       <c r="B7" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
         <v>127700029</v>
       </c>
       <c r="B11" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1705,7 +1705,7 @@
         <v>127700024</v>
       </c>
       <c r="B12" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1806,7 +1806,7 @@
         <v>127700026</v>
       </c>
       <c r="B13" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>127700030</v>
       </c>
       <c r="B14" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2008,7 +2008,7 @@
         <v>127700025</v>
       </c>
       <c r="B15" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2109,7 +2109,7 @@
         <v>127700021</v>
       </c>
       <c r="B16" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
